--- a/_docs/Trimestre_3/02_01_BBDD_Normalizacion/Ejemplo_Normalizacion_BBDD.xlsx
+++ b/_docs/Trimestre_3/02_01_BBDD_Normalizacion/Ejemplo_Normalizacion_BBDD.xlsx
@@ -1,13 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Downloads\Sistema_Gestion_Servicios_Tecnicos\_docs\Trimestre_3\02_01_BBDD_Normalizacion\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378F6E2D-D97D-43BC-9329-1D8D7F2C2C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sin Normalizar" sheetId="1" r:id="rId1"/>
+    <sheet name="Primera Forma" sheetId="2" r:id="rId2"/>
+    <sheet name="Segunda Forma" sheetId="3" r:id="rId3"/>
+    <sheet name="Tercera Forma" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,9 +27,404 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="129">
+  <si>
+    <t>Tecnico</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>Administrador</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Apellido</t>
+  </si>
+  <si>
+    <t>Numero</t>
+  </si>
+  <si>
+    <t>Correo</t>
+  </si>
+  <si>
+    <t>servicio</t>
+  </si>
+  <si>
+    <t>electrodomestico</t>
+  </si>
+  <si>
+    <t>orden de pago</t>
+  </si>
+  <si>
+    <t>pago</t>
+  </si>
+  <si>
+    <t>garantia</t>
+  </si>
+  <si>
+    <t>10/01/2025, Garantia completa, 10/12/2025, Enviar documentos para garantia, Vigente</t>
+  </si>
+  <si>
+    <t>12/05/2024, Garantia extendida, 10/12/2024, Enviar documentos para garantia, Sin vigencia</t>
+  </si>
+  <si>
+    <t>10/01/2022, Garantia completa, 10/12/2028, Enviar documentos para garantia, Vigente</t>
+  </si>
+  <si>
+    <t>$750.000, Efectivo, 12/12/2024</t>
+  </si>
+  <si>
+    <t>$1.000.000, Tarjeta de credito, 01/01/2025</t>
+  </si>
+  <si>
+    <t>$100.000, PayPal, 12/03/2024</t>
+  </si>
+  <si>
+    <t>12/12/2021, Pagado, $750.000</t>
+  </si>
+  <si>
+    <t>Estufa</t>
+  </si>
+  <si>
+    <t>Pepito</t>
+  </si>
+  <si>
+    <t>Ramirez</t>
+  </si>
+  <si>
+    <t>pep@gmail.com</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>Peñaloza</t>
+  </si>
+  <si>
+    <t>juan@gmai.com</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>Nandez</t>
+  </si>
+  <si>
+    <t>pedro@gmail.com</t>
+  </si>
+  <si>
+    <t>Luisa</t>
+  </si>
+  <si>
+    <t>Peralta</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>contraseña</t>
+  </si>
+  <si>
+    <t>estado</t>
+  </si>
+  <si>
+    <t>activo</t>
+  </si>
+  <si>
+    <t>inactivo</t>
+  </si>
+  <si>
+    <t>peral@gmail.com</t>
+  </si>
+  <si>
+    <t>Gomez</t>
+  </si>
+  <si>
+    <t>gg@gmail.com</t>
+  </si>
+  <si>
+    <t>Alan</t>
+  </si>
+  <si>
+    <t>Torres</t>
+  </si>
+  <si>
+    <t>at@gmail.com</t>
+  </si>
+  <si>
+    <t>Reparacion, Reparar, $70.000</t>
+  </si>
+  <si>
+    <t>Mantenimiento, No repara, $50.000</t>
+  </si>
+  <si>
+    <t>Reparacion, Reparar, $100.000</t>
+  </si>
+  <si>
+    <t>Marcus</t>
+  </si>
+  <si>
+    <t>Zeta</t>
+  </si>
+  <si>
+    <t>mz@gmail.com</t>
+  </si>
+  <si>
+    <t>Mateo</t>
+  </si>
+  <si>
+    <t>Mate</t>
+  </si>
+  <si>
+    <t>mt@gmail.com</t>
+  </si>
+  <si>
+    <t>Ron</t>
+  </si>
+  <si>
+    <t>Will</t>
+  </si>
+  <si>
+    <t>rw@gmail.com</t>
+  </si>
+  <si>
+    <t>orden de trabajo</t>
+  </si>
+  <si>
+    <t>solicitud de servicio</t>
+  </si>
+  <si>
+    <t>aprobada, 10/12/2020</t>
+  </si>
+  <si>
+    <t>Estufa, Whirpool, Nueva, Bien bonita</t>
+  </si>
+  <si>
+    <t>Nevera, Mabe, Nueva, Bien bonita</t>
+  </si>
+  <si>
+    <t>Lavadora, Haceb, Nueva, Bien bonita</t>
+  </si>
+  <si>
+    <t>cra 5, 12/12/2021, 12/12/2021, Finalizado, Sin observaciones, 5 estrellas, buen trabajo, 12/12/2021</t>
+  </si>
+  <si>
+    <t>cra 45, 12/12/2021, 12/12/2021, Finalizado, Sin observaciones, 5 estrellas, buen trabajo, 12/12/2021</t>
+  </si>
+  <si>
+    <t>cra 4, 12/12/2021, 12/12/2021, Finalizado, Sin observaciones, 5 estrellas, buen trabajo, 12/12/2021</t>
+  </si>
+  <si>
+    <t>Cliente Servicio y Pago</t>
+  </si>
+  <si>
+    <t>Tecnico y Orden de trabajo</t>
+  </si>
+  <si>
+    <t>Usuarios</t>
+  </si>
+  <si>
+    <t>Contraseña</t>
+  </si>
+  <si>
+    <t>Base de datos Servicio Tecnico</t>
+  </si>
+  <si>
+    <t>Rol</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Orden de trabajo</t>
+  </si>
+  <si>
+    <t>cra 5</t>
+  </si>
+  <si>
+    <t>Finalizado</t>
+  </si>
+  <si>
+    <t>Sin observaciones</t>
+  </si>
+  <si>
+    <t>5 estrellas</t>
+  </si>
+  <si>
+    <t>buen trabajo</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>cra 45</t>
+  </si>
+  <si>
+    <t>cra 4</t>
+  </si>
+  <si>
+    <t>Reparacion</t>
+  </si>
+  <si>
+    <t>Reparar</t>
+  </si>
+  <si>
+    <t>Pagado</t>
+  </si>
+  <si>
+    <t>Efectivo</t>
+  </si>
+  <si>
+    <t>Garantia completa</t>
+  </si>
+  <si>
+    <t>Enviar documentos para garantia</t>
+  </si>
+  <si>
+    <t>Vigente</t>
+  </si>
+  <si>
+    <t>aprobada</t>
+  </si>
+  <si>
+    <t>Bien bonita</t>
+  </si>
+  <si>
+    <t>Nueva</t>
+  </si>
+  <si>
+    <t>Whirpool</t>
+  </si>
+  <si>
+    <t>Mantenimiento</t>
+  </si>
+  <si>
+    <t>No repara</t>
+  </si>
+  <si>
+    <t>Nevera</t>
+  </si>
+  <si>
+    <t>Mabe</t>
+  </si>
+  <si>
+    <t>Tarjeta de credito</t>
+  </si>
+  <si>
+    <t>Garantia extendida</t>
+  </si>
+  <si>
+    <t>Sin vigencia</t>
+  </si>
+  <si>
+    <t>Lavadora</t>
+  </si>
+  <si>
+    <t>Haceb</t>
+  </si>
+  <si>
+    <t>PayPal</t>
+  </si>
+  <si>
+    <t>ID_Usuarios</t>
+  </si>
+  <si>
+    <t>Solicitud de Servicio</t>
+  </si>
+  <si>
+    <t>ID_Servcicio</t>
+  </si>
+  <si>
+    <t>ID_Electrodomestico</t>
+  </si>
+  <si>
+    <t>ID_Solicitud</t>
+  </si>
+  <si>
+    <t>ID_Orden_Trabajo</t>
+  </si>
+  <si>
+    <t>ID_Orden_Pago</t>
+  </si>
+  <si>
+    <t>ID_Pago</t>
+  </si>
+  <si>
+    <t>ID_Garantia</t>
+  </si>
+  <si>
+    <t>Instalacion</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Descripcion</t>
+  </si>
+  <si>
+    <t>Coste</t>
+  </si>
+  <si>
+    <t>Marca</t>
+  </si>
+  <si>
+    <t>Modelo</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>ID_Cliente</t>
+  </si>
+  <si>
+    <t>ID_Admin</t>
+  </si>
+  <si>
+    <t>ID_ELECTRODOMESTICO ID_SOLICITUD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID_Electrodomestico </t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Direccion</t>
+  </si>
+  <si>
+    <t>Fecha inicion</t>
+  </si>
+  <si>
+    <t>Fecha fin</t>
+  </si>
+  <si>
+    <t>Observaciones</t>
+  </si>
+  <si>
+    <t>Calificaicon</t>
+  </si>
+  <si>
+    <t>Reseña</t>
+  </si>
+  <si>
+    <t>Fecha reseña</t>
+  </si>
+  <si>
+    <t>12/122021</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +432,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -45,14 +469,100 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -330,9 +840,2979 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:M18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="5"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="1">
+        <v>654</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="1">
+        <v>987</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="1">
+        <v>321321</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="1">
+        <v>654</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="1">
+        <v>456</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="1">
+        <v>321</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="1">
+        <v>21321654987</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="1">
+        <v>987654</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="1">
+        <v>654987</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="1">
+        <v>654654</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="1">
+        <v>987654321</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="1">
+        <v>321321</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="1">
+        <v>987654</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="1">
+        <v>987546</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="1">
+        <v>2411132</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="1">
+        <v>654654</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="1">
+        <v>5445</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="1">
+        <v>123</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="B14:G14"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E10" r:id="rId1" xr:uid="{DAA289FB-471D-4B85-A566-591C5F395BC2}"/>
+    <hyperlink ref="E11" r:id="rId2" xr:uid="{CC6AC6CA-B284-45E9-A358-B61C90B2E060}"/>
+    <hyperlink ref="E12" r:id="rId3" xr:uid="{251929CB-2618-44C1-976B-2E2A45BA4DDC}"/>
+    <hyperlink ref="E16" r:id="rId4" xr:uid="{29027AE2-D409-4C2F-8A4B-5006EAC52C89}"/>
+    <hyperlink ref="E17" r:id="rId5" xr:uid="{56D3BD48-3C0B-4340-967C-5F442B83C90F}"/>
+    <hyperlink ref="E18" r:id="rId6" xr:uid="{35F2B361-AE78-419F-AFB6-B4B5A2832A6F}"/>
+    <hyperlink ref="E4" r:id="rId7" xr:uid="{C98A4EFC-4723-41F8-B237-A7732C9D399A}"/>
+    <hyperlink ref="E5" r:id="rId8" xr:uid="{E10F6C9E-1933-400B-BB44-83393D2EF86A}"/>
+    <hyperlink ref="E6" r:id="rId9" xr:uid="{1BF7296B-F0F1-4030-8E96-E06DAF98EBB3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAD2AE20-3024-418B-8BAE-A9E76C238F8A}">
+  <dimension ref="B2:P45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="5.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="5"/>
+    </row>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B3" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B4" s="6">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="1">
+        <v>987654</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="1">
+        <v>987546</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B5" s="6">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2411132</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="1">
+        <v>654654</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B6" s="6">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="1">
+        <v>5445</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="1">
+        <v>123</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B7" s="6">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="1">
+        <v>21321654987</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="1">
+        <v>987654</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B8" s="6">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="1">
+        <v>21321654987</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="1">
+        <v>987654</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J8" s="7">
+        <v>44542</v>
+      </c>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B9" s="6">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="1">
+        <v>21321654987</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="1">
+        <v>987654</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J9" s="7">
+        <v>44542</v>
+      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B10" s="6">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="1">
+        <v>21321654987</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="1">
+        <v>987654</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B11" s="6">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="1">
+        <v>21321654987</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="1">
+        <v>987654</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B12" s="6">
+        <v>4</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="1">
+        <v>21321654987</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="1">
+        <v>987654</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B13" s="6">
+        <v>4</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="1">
+        <v>21321654987</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="1">
+        <v>987654</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B14" s="6">
+        <v>4</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="1">
+        <v>21321654987</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="1">
+        <v>987654</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J14" s="7">
+        <v>44542</v>
+      </c>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B15" s="6">
+        <v>5</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="1">
+        <v>654987</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G15" s="1">
+        <v>654654</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B16" s="6">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="1">
+        <v>654987</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="1">
+        <v>654654</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J16" s="7">
+        <v>44542</v>
+      </c>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B17" s="6">
+        <v>5</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="1">
+        <v>654987</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="1">
+        <v>654654</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J17" s="7">
+        <v>44542</v>
+      </c>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B18" s="6">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="1">
+        <v>654987</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="1">
+        <v>654654</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B19" s="6">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="1">
+        <v>654987</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G19" s="1">
+        <v>654654</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B20" s="6">
+        <v>5</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="1">
+        <v>654987</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="1">
+        <v>654654</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B21" s="6">
+        <v>5</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="1">
+        <v>654987</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="1">
+        <v>654654</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B22" s="6">
+        <v>5</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="1">
+        <v>654987</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G22" s="1">
+        <v>654654</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J22" s="7">
+        <v>44542</v>
+      </c>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B23" s="6">
+        <v>6</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="1">
+        <v>987654321</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G23" s="1">
+        <v>321321</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B24" s="6">
+        <v>6</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="1">
+        <v>987654321</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="1">
+        <v>321321</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J24" s="7">
+        <v>44542</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B25" s="6">
+        <v>6</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="1">
+        <v>987654321</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G25" s="1">
+        <v>321321</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J25" s="7">
+        <v>44542</v>
+      </c>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B26" s="6">
+        <v>6</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="1">
+        <v>987654321</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="1">
+        <v>321321</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B27" s="6">
+        <v>6</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" s="1">
+        <v>987654321</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" s="1">
+        <v>321321</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B28" s="6">
+        <v>6</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" s="1">
+        <v>987654321</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="1">
+        <v>321321</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B29" s="6">
+        <v>6</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="1">
+        <v>987654321</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" s="1">
+        <v>321321</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B30" s="6">
+        <v>6</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="1">
+        <v>987654321</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" s="1">
+        <v>321321</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J30" s="7">
+        <v>44542</v>
+      </c>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B31" s="6">
+        <v>7</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="1">
+        <v>654</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G31" s="1">
+        <v>987</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N31" s="7">
+        <v>44542</v>
+      </c>
+      <c r="O31" s="10">
+        <v>750000</v>
+      </c>
+      <c r="P31" s="7">
+        <v>45667</v>
+      </c>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B32" s="6">
+        <v>7</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="1">
+        <v>654</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G32" s="1">
+        <v>987</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="M32" s="7">
+        <v>44175</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B33" s="6">
+        <v>7</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="1">
+        <v>654</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G33" s="1">
+        <v>987</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="10">
+        <v>70000</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M33" s="1"/>
+      <c r="N33" s="10">
+        <v>750000</v>
+      </c>
+      <c r="O33" s="7">
+        <v>45638</v>
+      </c>
+      <c r="P33" s="7">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B34" s="6">
+        <v>7</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="1">
+        <v>654</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G34" s="1">
+        <v>987</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B35" s="6">
+        <v>7</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" s="1">
+        <v>654</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G35" s="1">
+        <v>987</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I35" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B36" s="6">
+        <v>8</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E36" s="1">
+        <v>321321</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G36" s="1">
+        <v>654</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N36" s="7">
+        <v>44542</v>
+      </c>
+      <c r="O36" s="10">
+        <v>1000000</v>
+      </c>
+      <c r="P36" s="7">
+        <v>45424</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B37" s="6">
+        <v>8</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E37" s="1">
+        <v>321321</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G37" s="1">
+        <v>654</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="M37" s="7">
+        <v>44175</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B38" s="6">
+        <v>8</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E38" s="1">
+        <v>321321</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G38" s="1">
+        <v>654</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J38" s="1"/>
+      <c r="K38" s="10">
+        <v>50000</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M38" s="1"/>
+      <c r="N38" s="10">
+        <v>750000</v>
+      </c>
+      <c r="O38" s="7">
+        <v>45658</v>
+      </c>
+      <c r="P38" s="7">
+        <v>45636</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B39" s="6">
+        <v>8</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E39" s="1">
+        <v>321321</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G39" s="1">
+        <v>654</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I39" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B40" s="6">
+        <v>8</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="1">
+        <v>321321</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G40" s="1">
+        <v>654</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B41" s="6">
+        <v>9</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" s="1">
+        <v>456</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G41" s="1">
+        <v>321</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I41" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="N41" s="7">
+        <v>44542</v>
+      </c>
+      <c r="O41" s="10">
+        <v>100000</v>
+      </c>
+      <c r="P41" s="7">
+        <v>44571</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B42" s="6">
+        <v>9</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E42" s="1">
+        <v>456</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G42" s="1">
+        <v>321</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I42" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="L42" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="M42" s="7">
+        <v>44175</v>
+      </c>
+      <c r="N42" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="O42" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B43" s="6">
+        <v>9</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E43" s="1">
+        <v>456</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G43" s="1">
+        <v>321</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I43" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" s="10">
+        <v>100000</v>
+      </c>
+      <c r="L43" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="M43" s="1"/>
+      <c r="N43" s="10">
+        <v>750000</v>
+      </c>
+      <c r="O43" s="7">
+        <v>45363</v>
+      </c>
+      <c r="P43" s="7">
+        <v>47097</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B44" s="6">
+        <v>9</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44" s="1">
+        <v>456</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G44" s="1">
+        <v>321</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B45" s="6">
+        <v>9</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="1">
+        <v>456</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G45" s="1">
+        <v>321</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I45" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:P2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F4" r:id="rId1" xr:uid="{AC2AEFFA-ED3B-409E-BFD2-C7F3FF567C2C}"/>
+    <hyperlink ref="F5" r:id="rId2" xr:uid="{1E1475B6-B19E-4D50-8E0A-4021B645F632}"/>
+    <hyperlink ref="F6" r:id="rId3" xr:uid="{3C5D449C-62DA-4BCB-A1D3-9F9AE85FED67}"/>
+    <hyperlink ref="F7" r:id="rId4" xr:uid="{6541AA01-D1DB-4DA5-B265-FE9E8FA27F72}"/>
+    <hyperlink ref="F15" r:id="rId5" xr:uid="{2300A5DB-1B3D-4FA9-8C51-B8E390374BAF}"/>
+    <hyperlink ref="F23" r:id="rId6" xr:uid="{451897D1-3CEC-4A37-B788-4400A47C6B54}"/>
+    <hyperlink ref="F31" r:id="rId7" xr:uid="{CAFD8BDA-4C13-4D07-9F3D-0FFBDBDFDFFA}"/>
+    <hyperlink ref="F36" r:id="rId8" xr:uid="{0302D1BE-688E-4C55-A5CD-1B970B7530FC}"/>
+    <hyperlink ref="F41" r:id="rId9" xr:uid="{C1745D84-3540-4334-AAD5-EE67C42E35C4}"/>
+    <hyperlink ref="F8" r:id="rId10" xr:uid="{A0A8B079-9192-414A-A004-C9333B7503AD}"/>
+    <hyperlink ref="F9" r:id="rId11" xr:uid="{36A12BF3-5803-4EDD-A17F-F57289367D18}"/>
+    <hyperlink ref="F10" r:id="rId12" xr:uid="{C8567956-F91E-4D6A-8294-EAE3BE693C07}"/>
+    <hyperlink ref="F11" r:id="rId13" xr:uid="{B008BF06-91BB-410C-9078-95789EC123F2}"/>
+    <hyperlink ref="F12" r:id="rId14" xr:uid="{C5843587-2C14-4BB6-A6EC-5A79C7D7CCD6}"/>
+    <hyperlink ref="F13" r:id="rId15" xr:uid="{A1A774DE-2743-4D3E-880E-E800BA0CF1C4}"/>
+    <hyperlink ref="F14" r:id="rId16" xr:uid="{790AEB6D-34E4-4368-BBA1-2A9006EF26E6}"/>
+    <hyperlink ref="F16" r:id="rId17" xr:uid="{F1397AD7-EECD-4639-8FB5-65E372EE0BB1}"/>
+    <hyperlink ref="F17" r:id="rId18" xr:uid="{ACFCECC9-536B-4A71-9023-AAD56E48C10A}"/>
+    <hyperlink ref="F18" r:id="rId19" xr:uid="{477EE755-BAC3-4C72-8A62-F03909DFD62D}"/>
+    <hyperlink ref="F19" r:id="rId20" xr:uid="{520D2252-283E-4F60-8747-1D80B6A9A437}"/>
+    <hyperlink ref="F20" r:id="rId21" xr:uid="{A2485DAC-8678-4F6E-847A-86689B91A161}"/>
+    <hyperlink ref="F21" r:id="rId22" xr:uid="{8A9C0FD5-CF27-4EEA-8C23-F85D5D2A46A2}"/>
+    <hyperlink ref="F22" r:id="rId23" xr:uid="{857761D2-16DD-46F5-9B30-6E0A52B18B0F}"/>
+    <hyperlink ref="F24" r:id="rId24" xr:uid="{0E3820C5-5D2E-4C76-AE4F-D0DB84136131}"/>
+    <hyperlink ref="F25" r:id="rId25" xr:uid="{4217921A-0A66-4DC9-AE8E-7614FB1B10DE}"/>
+    <hyperlink ref="F26" r:id="rId26" xr:uid="{C1C02594-2971-4DE3-A733-E7C60D9E5677}"/>
+    <hyperlink ref="F27" r:id="rId27" xr:uid="{FD2BD049-65E6-4F2C-A9D5-6D4329726F77}"/>
+    <hyperlink ref="F28" r:id="rId28" xr:uid="{0F9135F9-0794-47B3-9607-368A8C3A11B1}"/>
+    <hyperlink ref="F29" r:id="rId29" xr:uid="{5702B9F7-2DF2-48DB-AE50-44B412953DD3}"/>
+    <hyperlink ref="F30" r:id="rId30" xr:uid="{AAA6BD0E-DF88-468B-84A4-82E9F1ABFDD2}"/>
+    <hyperlink ref="F32" r:id="rId31" xr:uid="{BD69117F-75AC-45B8-8ADD-7EABADAB1B6D}"/>
+    <hyperlink ref="F33" r:id="rId32" xr:uid="{F1E20E57-645C-46C9-A239-3D58EF425A18}"/>
+    <hyperlink ref="F34" r:id="rId33" xr:uid="{5D9B3CB2-5D67-432D-8F48-DF0F0541A9EE}"/>
+    <hyperlink ref="F35" r:id="rId34" xr:uid="{F19EA250-937F-4707-B143-960F8FE02B8D}"/>
+    <hyperlink ref="F37:F40" r:id="rId35" display="mt@gmail.com" xr:uid="{BA880131-21EB-4FAD-A566-09E93E638235}"/>
+    <hyperlink ref="F42" r:id="rId36" xr:uid="{C59CD138-D1B7-4C0A-BFBF-636840AF526F}"/>
+    <hyperlink ref="F43" r:id="rId37" xr:uid="{4BFE8E91-A8CC-4B05-B8E7-452A24C9E8CB}"/>
+    <hyperlink ref="F44" r:id="rId38" xr:uid="{212ED538-13C0-47FF-92CF-615DDBB45721}"/>
+    <hyperlink ref="F45" r:id="rId39" xr:uid="{A9408A48-289E-4ECD-8BF1-32217505F65F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F148E26-4639-479C-B5D1-CD642533D3CB}">
+  <dimension ref="B2:J54"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B2" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B3" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="6">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="1">
+        <v>987654</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="1">
+        <v>987546</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B5" s="6">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2411132</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="1">
+        <v>654654</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B6" s="6">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="1">
+        <v>5445</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="1">
+        <v>123</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B7" s="6">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="1">
+        <v>21321654987</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="1">
+        <v>987654</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B8" s="6">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="1">
+        <v>654987</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="1">
+        <v>654654</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B9" s="6">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="1">
+        <v>987654321</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="1">
+        <v>321321</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="6">
+        <v>7</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="1">
+        <v>654</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="1">
+        <v>987</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B11" s="6">
+        <v>8</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="1">
+        <v>321321</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="1">
+        <v>654</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B12" s="6">
+        <v>9</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="1">
+        <v>456</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G12" s="1">
+        <v>321</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="6">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="1">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="6">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="1">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="6">
+        <v>3</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="1">
+        <v>100000</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="I18" s="12"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="H19" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="13"/>
+      <c r="H20" s="6">
+        <v>1</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="H21" s="6">
+        <v>2</v>
+      </c>
+      <c r="I21" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="6">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H22" s="6">
+        <v>3</v>
+      </c>
+      <c r="I22" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="6">
+        <v>2</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="6">
+        <v>3</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="13"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="6">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D28" s="7">
+        <v>44175</v>
+      </c>
+      <c r="E28" s="1">
+        <v>7</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="6">
+        <v>2</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D29" s="7">
+        <v>44175</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="6">
+        <v>3</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" s="7">
+        <v>44175</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C31" s="8"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B33" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" s="6">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="7">
+        <v>44542</v>
+      </c>
+      <c r="E34" s="7">
+        <v>44542</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J34" s="7">
+        <v>44542</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="6">
+        <v>2</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="7">
+        <v>44542</v>
+      </c>
+      <c r="E35" s="7">
+        <v>44542</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J35" s="7">
+        <v>44542</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B36" s="6">
+        <v>3</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" s="7">
+        <v>44542</v>
+      </c>
+      <c r="E36" s="7">
+        <v>44542</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J36" s="7">
+        <v>44542</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B38" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="6">
+        <v>1</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E40" s="1">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="6">
+        <v>2</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" s="1">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" s="6">
+        <v>3</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E42" s="1">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C43" s="9"/>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B45" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" s="6">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1">
+        <v>750000</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46" s="7">
+        <v>45638</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B47" s="6">
+        <v>2</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E47" s="7">
+        <v>45658</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B48" s="6">
+        <v>3</v>
+      </c>
+      <c r="C48" s="1">
+        <v>100000</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E48" s="7">
+        <v>45363</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="6">
+        <v>1</v>
+      </c>
+      <c r="C52" s="7">
+        <v>45638</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E52" s="1">
+        <v>46001</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B53" s="6">
+        <v>2</v>
+      </c>
+      <c r="C53" s="7">
+        <v>45424</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E53" s="1">
+        <v>45636</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B54" s="6">
+        <v>3</v>
+      </c>
+      <c r="C54" s="7">
+        <v>44571</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E54" s="1">
+        <v>47097</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="G32:J32"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B44:E44"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F4" r:id="rId1" xr:uid="{D5545526-0189-4168-9FE8-AE7A30E045A8}"/>
+    <hyperlink ref="F5" r:id="rId2" xr:uid="{0A4C2CFE-C65D-445A-A096-EBBF60D75D78}"/>
+    <hyperlink ref="F6" r:id="rId3" xr:uid="{6887E201-3742-4A82-AEED-A88B861875CD}"/>
+    <hyperlink ref="F7" r:id="rId4" xr:uid="{8AE6A629-6D1A-4766-80C6-D3F17B1DEAC7}"/>
+    <hyperlink ref="F8" r:id="rId5" xr:uid="{73EC4E40-5281-4292-B9C6-FBE48F81BE86}"/>
+    <hyperlink ref="F9" r:id="rId6" xr:uid="{CB1F15CF-8A41-4873-9B03-D92CDE1CE849}"/>
+    <hyperlink ref="F10" r:id="rId7" xr:uid="{52462A85-54AC-45B1-BABD-80D73247AEAA}"/>
+    <hyperlink ref="F11" r:id="rId8" xr:uid="{B3BB6FBC-BE00-4B20-960B-C9AF78D07313}"/>
+    <hyperlink ref="F12" r:id="rId9" xr:uid="{BF17BC89-2895-4C42-AEE2-0D8CFC85EDA7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA9FA88-3A40-4A37-A515-9CFA906432A7}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+  </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
